--- a/Hardware/BMS_V4/BOM/BMS_V4.02_BOM.xlsx
+++ b/Hardware/BMS_V4/BOM/BMS_V4.02_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Electronics_Solaris\BMS Version 4\Hardware\BMS_V4\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EC593D-C958-41AF-B9E1-AF4F669AFCC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A7EEAA-35EC-4A3A-BAD8-AABD4FFD25E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="452">
   <si>
     <t>BMS v4.02 - Bill of Materials</t>
   </si>
@@ -116,9 +116,6 @@
     <t>Özdisan</t>
   </si>
   <si>
-    <t>BAT pin. Not stocked: the 0805 CL21Y105KCFVPJE (in stock) can be hand-soldered on these 1206 pads</t>
-  </si>
-  <si>
     <t>C2, C9, C12, C13, C14, C16, C18, C20, C23, C38</t>
   </si>
   <si>
@@ -278,9 +275,6 @@
     <t>CL21C300JBANNNC</t>
   </si>
   <si>
-    <t>CAN_H/CAN_L filter. Not stocked (33pF neither); 47pF CL21C470JBANNNC is in stock if you accept the change</t>
-  </si>
-  <si>
     <t>C26</t>
   </si>
   <si>
@@ -299,9 +293,6 @@
     <t>KB3D332KL518Y</t>
   </si>
   <si>
-    <t>CAN shield to ISO_GND. Not stocked: any 3.3nF &gt;= 1kV disc, 5 mm pitch</t>
-  </si>
-  <si>
     <t>C27</t>
   </si>
   <si>
@@ -344,9 +335,6 @@
     <t>CL31B225KCHSNNE</t>
   </si>
   <si>
-    <t>LM5163 input. Not stocked (TDK/Murata/Yageo 1206 2.2uF 100V neither): request</t>
-  </si>
-  <si>
     <t>C32, C34</t>
   </si>
   <si>
@@ -374,9 +362,6 @@
     <t>MCF05JTN500560</t>
   </si>
   <si>
-    <t>LM5163 ripple injection. Not stocked (Samsung/Yageo 56pF neither): request</t>
-  </si>
-  <si>
     <t>C35</t>
   </si>
   <si>
@@ -452,9 +437,6 @@
     <t>BAT46W-7-F</t>
   </si>
   <si>
-    <t>BAT supply. Not stocked (Vishay BAT46W-E3-08 neither): request</t>
-  </si>
-  <si>
     <t>D2</t>
   </si>
   <si>
@@ -689,9 +671,6 @@
     <t>2EDGVC-5.08-04P-14-00AH</t>
   </si>
   <si>
-    <t>Footprint is Phoenix MSTBVA 2,5/4-G-5,08. Not stocked in any colour: request</t>
-  </si>
-  <si>
     <t>J6</t>
   </si>
   <si>
@@ -710,9 +689,6 @@
     <t>DS1013-10SSIB1</t>
   </si>
   <si>
-    <t>ST-Link V2 clone pinout. Not stocked: any 2x5 2.54mm box header</t>
-  </si>
-  <si>
     <t>J7, J8</t>
   </si>
   <si>
@@ -818,9 +794,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>Was 1S4E_1505S1U (15 V input). Not at Özdisan: RECOM RFM-0505S is a SIP4 alternative, check pinout</t>
-  </si>
-  <si>
     <t>Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8, Q9, Q10, Q11, Q12, Q13, Q14, Q15, Q16</t>
   </si>
   <si>
@@ -1067,9 +1040,6 @@
     <t>10k 1%</t>
   </si>
   <si>
-    <t>Resistor 0805 10k 1%</t>
-  </si>
-  <si>
     <t>0805S8F1002T5E</t>
   </si>
   <si>
@@ -1100,9 +1070,6 @@
     <t>HP122WJ0220T4E</t>
   </si>
   <si>
-    <t>Balance resistor. No 22R 2W 2512 stocked: request (any 2512 22R &gt;= 2W fits)</t>
-  </si>
-  <si>
     <t>R43</t>
   </si>
   <si>
@@ -1115,9 +1082,6 @@
     <t>0805S8F0000TDE</t>
   </si>
   <si>
-    <t>GND to cell 0 (remove on the lower board if GND is wired to TP2). No 0805 0R stocked: a solder bridge works</t>
-  </si>
-  <si>
     <t>R97</t>
   </si>
   <si>
@@ -1187,9 +1151,6 @@
     <t>TSM2A103F3951RZ</t>
   </si>
   <si>
-    <t>On-board temperature (BQ TS1-TS3). Not stocked (Murata NCP21XV103J03RA neither): request</t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
@@ -1205,9 +1166,6 @@
     <t>BQ76952PFBR</t>
   </si>
   <si>
-    <t>Not stocked: request (or reuse parts you already have)</t>
-  </si>
-  <si>
     <t>U2</t>
   </si>
   <si>
@@ -1392,13 +1350,58 @@
   </si>
   <si>
     <t>Red stock cell = Özdisan has fewer than needed for the board count above (use "Request Price &amp; Stock" or another supplier).</t>
+  </si>
+  <si>
+    <t>Resistor 0805 10k  0.1%</t>
+  </si>
+  <si>
+    <t>BAT pin. Not stocked: the 0805 CL21Y105KCFVPJE (in stock) can be hand-soldered on these 1206 pads.(805 added because there was np stock.)</t>
+  </si>
+  <si>
+    <t>CAN_H/CAN_L filter. Not stocked (33pF neither); 47pF CL21C470JBANNNC is in stock if you accept the change. 27pf added.</t>
+  </si>
+  <si>
+    <t>CAN shield to ISO_GND. Not stocked: any 3.3nF &gt;= 1kV disc, 5 mm pitch(We have it)</t>
+  </si>
+  <si>
+    <t>LM5163 input. Not stocked (TDK/Murata/Yageo 1206 2.2uF 100V neither): (1210 added, we can solder)</t>
+  </si>
+  <si>
+    <t>LM5163 ripple injection. Not stocked (Samsung/Yageo 56pF neither): request(0603 added)</t>
+  </si>
+  <si>
+    <t>BAT supply. Not stocked (Vishay BAT46W-E3-08 neither): (200ma added)</t>
+  </si>
+  <si>
+    <t>Footprint is Phoenix MSTBVA 2,5/4-G-5,08. Not stocked in any colour: (paramteric added)</t>
+  </si>
+  <si>
+    <t>ST-Link V2 clone pinout. Not stocked: any 2x5 2.54mm box header(we have it)</t>
+  </si>
+  <si>
+    <t>Was 1S4E_1505S1U (15 V input). Not at Özdisan: RECOM RFM-0505S is a SIP4 alternative, check pinout.(not nedded right now)</t>
+  </si>
+  <si>
+    <t>Balance resistor. No 22R 2W 2512 stocked: request (any 2512 22R &gt;= 2W fits)(3w 10r added)</t>
+  </si>
+  <si>
+    <t>GND to cell 0 (remove on the lower board if GND is wired to TP2). No 0805 0R stocked: a solder bridge works(no need)</t>
+  </si>
+  <si>
+    <t>On-board temperature (BQ TS1-TS3). Not stocked (Murata NCP21XV103J03RA neither): (the alternative will wok for now)</t>
+  </si>
+  <si>
+    <t>Ekom</t>
+  </si>
+  <si>
+    <t>The correct IC is with SPI whic is BQ7695203</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1457,6 +1460,27 @@
       <name val="Arial"/>
       <charset val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1499,10 +1523,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1545,14 +1570,36 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1830,30 +1877,30 @@
     <col min="10" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="12" customWidth="1"/>
-    <col min="15" max="15" width="60" customWidth="1"/>
+    <col min="15" max="15" width="63.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="A2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1910,7 +1957,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>1</v>
       </c>
@@ -1935,17 +1982,17 @@
       <c r="H6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
+      <c r="I6" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="4">
+        <v>60000</v>
       </c>
       <c r="K6" s="8">
-        <v>3.2257699999999998</v>
+        <v>11.8782</v>
       </c>
       <c r="L6" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4">
         <f t="shared" ref="M6:M37" si="0">IF(L6="",C6*$C$3,MAX(C6*$C$3,L6))</f>
@@ -1953,10 +2000,10 @@
       </c>
       <c r="N6" s="8">
         <f t="shared" ref="N6:N37" si="1">IF(K6="","",K6*M6)</f>
-        <v>6.4515399999999996</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>25</v>
+        <v>23.756399999999999</v>
+      </c>
+      <c r="O6" s="18" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -1964,25 +2011,25 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4">
         <v>10</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>24</v>
@@ -2005,7 +2052,7 @@
         <v>13.8408</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -2013,7 +2060,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4">
         <v>1</v>
@@ -2022,16 +2069,16 @@
         <v>19</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>24</v>
@@ -2054,7 +2101,7 @@
         <v>23.703399999999998</v>
       </c>
       <c r="O8" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -2062,25 +2109,25 @@
         <v>4</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>24</v>
@@ -2103,7 +2150,7 @@
         <v>6.0916000000000006</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -2111,25 +2158,25 @@
         <v>5</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="4">
         <v>3</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="F10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>24</v>
@@ -2152,7 +2199,7 @@
         <v>6.9989999999999997</v>
       </c>
       <c r="O10" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -2160,25 +2207,25 @@
         <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>24</v>
@@ -2201,7 +2248,7 @@
         <v>10.37025</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -2209,25 +2256,25 @@
         <v>7</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="4">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="F12" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>24</v>
@@ -2256,25 +2303,25 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="4">
         <v>2</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>24</v>
@@ -2297,7 +2344,7 @@
         <v>99.254400000000004</v>
       </c>
       <c r="O13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -2305,25 +2352,25 @@
         <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="4">
         <v>2</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>63</v>
-      </c>
       <c r="F14" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>24</v>
@@ -2352,25 +2399,25 @@
         <v>10</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C15" s="4">
         <v>2</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>24</v>
@@ -2393,7 +2440,7 @@
         <v>5.9879999999999995</v>
       </c>
       <c r="O15" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -2401,25 +2448,25 @@
         <v>11</v>
       </c>
       <c r="B16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="4">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="F16" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>24</v>
@@ -2448,33 +2495,35 @@
         <v>12</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C17" s="4">
         <v>2</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="7">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8"/>
+        <v>77</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="4">
+        <v>695000</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0.88336000000000003</v>
+      </c>
       <c r="L17" s="4">
         <v>10</v>
       </c>
@@ -2482,12 +2531,12 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="N17" s="8" t="str">
+      <c r="N17" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>79</v>
+        <v>8.8336000000000006</v>
+      </c>
+      <c r="O17" s="18" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -2495,25 +2544,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="4">
-        <v>1</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>24</v>
@@ -2536,7 +2585,7 @@
         <v>25.890599999999999</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>86</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -2544,25 +2593,25 @@
         <v>14</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="4">
+        <v>1</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="4">
-        <v>1</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>24</v>
@@ -2585,7 +2634,7 @@
         <v>8.8139000000000003</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -2593,25 +2642,25 @@
         <v>15</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C20" s="4">
         <v>2</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>24</v>
@@ -2640,16 +2689,16 @@
         <v>16</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C21" s="4">
         <v>1</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>21</v>
@@ -2658,16 +2707,16 @@
         <v>22</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J21" s="7">
-        <v>0</v>
+        <v>97</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J21" s="21">
+        <v>1200</v>
       </c>
       <c r="K21" s="8">
-        <v>11.815899999999999</v>
+        <v>16.57</v>
       </c>
       <c r="L21" s="4">
         <v>1</v>
@@ -2678,10 +2727,10 @@
       </c>
       <c r="N21" s="8">
         <f t="shared" si="1"/>
-        <v>23.631799999999998</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>101</v>
+        <v>33.14</v>
+      </c>
+      <c r="O21" s="18" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -2689,25 +2738,25 @@
         <v>17</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C22" s="4">
         <v>2</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>24</v>
@@ -2730,7 +2779,7 @@
         <v>6.5666000000000002</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -2738,34 +2787,34 @@
         <v>18</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="4">
         <v>1</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J23" s="7">
-        <v>0</v>
+        <v>106</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J23" s="21">
+        <v>8800</v>
       </c>
       <c r="K23" s="8">
-        <v>0.32833000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="L23" s="4">
         <v>20</v>
@@ -2776,10 +2825,10 @@
       </c>
       <c r="N23" s="8">
         <f t="shared" si="1"/>
-        <v>6.5666000000000002</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>111</v>
+        <v>7.6</v>
+      </c>
+      <c r="O23" s="18" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -2787,25 +2836,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C24" s="4">
         <v>1</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>21</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>24</v>
@@ -2828,7 +2877,7 @@
         <v>118.4436</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -2836,25 +2885,25 @@
         <v>20</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C25" s="4">
         <v>2</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>24</v>
@@ -2877,7 +2926,7 @@
         <v>245.0728</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
@@ -2885,25 +2934,25 @@
         <v>21</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C26" s="4">
         <v>17</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>22</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>24</v>
@@ -2926,7 +2975,7 @@
         <v>24.55208</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -2934,48 +2983,48 @@
         <v>22</v>
       </c>
       <c r="B27" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C27" s="4">
+        <v>1</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C27" s="4">
-        <v>1</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J27" s="7">
-        <v>0</v>
+      <c r="I27" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="21">
+        <v>10000</v>
       </c>
       <c r="K27" s="8">
-        <v>3.1537199999999999</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="L27" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M27" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N27" s="8">
         <f t="shared" si="1"/>
-        <v>6.3074399999999997</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>137</v>
+        <v>11.6</v>
+      </c>
+      <c r="O27" s="18" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -2983,25 +3032,25 @@
         <v>23</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C28" s="4">
         <v>1</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>24</v>
@@ -3024,7 +3073,7 @@
         <v>5.4633000000000003</v>
       </c>
       <c r="O28" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -3032,25 +3081,25 @@
         <v>24</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C29" s="4">
         <v>1</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>24</v>
@@ -3073,7 +3122,7 @@
         <v>7.8115999999999994</v>
       </c>
       <c r="O29" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
@@ -3081,25 +3130,25 @@
         <v>25</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C30" s="4">
         <v>16</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>24</v>
@@ -3122,7 +3171,7 @@
         <v>54.055039999999998</v>
       </c>
       <c r="O30" s="5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
@@ -3130,25 +3179,25 @@
         <v>26</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C31" s="4">
         <v>16</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>24</v>
@@ -3171,33 +3220,33 @@
         <v>25.75648</v>
       </c>
       <c r="O31" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>27</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C32" s="4">
         <v>1</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>24</v>
@@ -3220,7 +3269,7 @@
         <v>21.592349999999996</v>
       </c>
       <c r="O32" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -3228,25 +3277,25 @@
         <v>28</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>24</v>
@@ -3269,7 +3318,7 @@
         <v>86.991</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -3277,25 +3326,25 @@
         <v>29</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C34" s="4">
         <v>1</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>24</v>
@@ -3318,7 +3367,7 @@
         <v>336.46600000000001</v>
       </c>
       <c r="O34" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -3326,25 +3375,25 @@
         <v>30</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C35" s="4">
         <v>1</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>24</v>
@@ -3367,7 +3416,7 @@
         <v>21.344999999999999</v>
       </c>
       <c r="O35" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -3375,25 +3424,25 @@
         <v>31</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>24</v>
@@ -3416,7 +3465,7 @@
         <v>27.1858</v>
       </c>
       <c r="O36" s="5" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
@@ -3424,25 +3473,25 @@
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C37" s="4">
         <v>1</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>24</v>
@@ -3465,7 +3514,7 @@
         <v>12.83864</v>
       </c>
       <c r="O37" s="5" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -3473,25 +3522,25 @@
         <v>33</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I38" s="6" t="s">
         <v>24</v>
@@ -3514,7 +3563,7 @@
         <v>6.4193199999999999</v>
       </c>
       <c r="O38" s="5" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -3522,34 +3571,34 @@
         <v>34</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C39" s="4">
         <v>1</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J39" s="7">
-        <v>0</v>
-      </c>
-      <c r="K39" s="8">
-        <v>3.20966</v>
+        <v>209</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J39" s="21">
+        <v>242</v>
+      </c>
+      <c r="K39" s="22">
+        <v>5.5145900000000001</v>
       </c>
       <c r="L39" s="4">
         <v>1</v>
@@ -3560,36 +3609,36 @@
       </c>
       <c r="N39" s="8">
         <f t="shared" si="3"/>
-        <v>6.4193199999999999</v>
-      </c>
-      <c r="O39" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+        <v>11.02918</v>
+      </c>
+      <c r="O39" s="18" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>35</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C40" s="4">
         <v>1</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>24</v>
@@ -3611,8 +3660,8 @@
         <f t="shared" si="3"/>
         <v>4.3559599999999996</v>
       </c>
-      <c r="O40" s="5" t="s">
-        <v>223</v>
+      <c r="O40" s="18" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -3620,25 +3669,25 @@
         <v>36</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C41" s="4">
         <v>2</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="I41" s="6" t="s">
         <v>24</v>
@@ -3661,7 +3710,7 @@
         <v>19.257960000000001</v>
       </c>
       <c r="O41" s="5" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
@@ -3669,25 +3718,25 @@
         <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="C42" s="4">
         <v>2</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="I42" s="6" t="s">
         <v>24</v>
@@ -3710,7 +3759,7 @@
         <v>60.112400000000001</v>
       </c>
       <c r="O42" s="5" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
@@ -3718,25 +3767,25 @@
         <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="C43" s="4">
         <v>2</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="I43" s="6" t="s">
         <v>24</v>
@@ -3759,7 +3808,7 @@
         <v>26.393319999999999</v>
       </c>
       <c r="O43" s="5" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
@@ -3767,25 +3816,25 @@
         <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C44" s="4">
         <v>1</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="I44" s="6" t="s">
         <v>24</v>
@@ -3814,25 +3863,25 @@
         <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>24</v>
@@ -3855,7 +3904,7 @@
         <v>15.45134</v>
       </c>
       <c r="O45" s="5" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="46" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -3863,25 +3912,25 @@
         <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="C46" s="4">
         <v>1</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>257</v>
+        <v>248</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>249</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="7"/>
@@ -3895,8 +3944,8 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="O46" s="5" t="s">
-        <v>259</v>
+      <c r="O46" s="18" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="47" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -3904,25 +3953,25 @@
         <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C47" s="4">
         <v>16</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>24</v>
@@ -3945,7 +3994,7 @@
         <v>445.28640000000001</v>
       </c>
       <c r="O47" s="5" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
@@ -3953,25 +4002,25 @@
         <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C48" s="4">
         <v>8</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>24</v>
@@ -3994,7 +4043,7 @@
         <v>7.5509999999999993</v>
       </c>
       <c r="O48" s="5" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
@@ -4002,25 +4051,25 @@
         <v>44</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C49" s="4">
         <v>7</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>24</v>
@@ -4049,25 +4098,25 @@
         <v>45</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C50" s="4">
         <v>1</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>24</v>
@@ -4090,7 +4139,7 @@
         <v>114.54859999999999</v>
       </c>
       <c r="O50" s="5" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
@@ -4098,25 +4147,25 @@
         <v>46</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C51" s="4">
         <v>3</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>24</v>
@@ -4145,25 +4194,25 @@
         <v>47</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="C52" s="4">
         <v>17</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>24</v>
@@ -4186,7 +4235,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O52" s="5" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
@@ -4194,25 +4243,25 @@
         <v>48</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="C53" s="4">
         <v>1</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I53" s="6" t="s">
         <v>24</v>
@@ -4235,7 +4284,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O53" s="5" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
@@ -4243,25 +4292,25 @@
         <v>49</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C54" s="4">
         <v>1</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="I54" s="6" t="s">
         <v>24</v>
@@ -4284,7 +4333,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O54" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
@@ -4292,25 +4341,25 @@
         <v>50</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C55" s="4">
         <v>1</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="I55" s="6" t="s">
         <v>24</v>
@@ -4339,25 +4388,25 @@
         <v>51</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="C56" s="4">
         <v>2</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="I56" s="6" t="s">
         <v>24</v>
@@ -4380,7 +4429,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O56" s="5" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
@@ -4388,25 +4437,25 @@
         <v>52</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C57" s="4">
         <v>1</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>24</v>
@@ -4429,7 +4478,7 @@
         <v>8.3155000000000001</v>
       </c>
       <c r="O57" s="5" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
@@ -4437,25 +4486,25 @@
         <v>53</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C58" s="4">
         <v>1</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>24</v>
@@ -4478,7 +4527,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O58" s="5" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
@@ -4486,25 +4535,25 @@
         <v>54</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C59" s="4">
         <v>1</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="I59" s="6" t="s">
         <v>24</v>
@@ -4527,7 +4576,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O59" s="5" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
@@ -4535,25 +4584,25 @@
         <v>55</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="C60" s="4">
         <v>1</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>24</v>
@@ -4576,7 +4625,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O60" s="5" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
@@ -4584,25 +4633,25 @@
         <v>56</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C61" s="4">
         <v>18</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>24</v>
@@ -4625,7 +4674,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O61" s="5" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
@@ -4633,48 +4682,48 @@
         <v>57</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C62" s="4">
         <v>1</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>342</v>
+        <v>332</v>
+      </c>
+      <c r="E62" s="18" t="s">
+        <v>437</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J62" s="7">
-        <v>0</v>
+        <v>333</v>
+      </c>
+      <c r="I62" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="4">
+        <v>2400</v>
       </c>
       <c r="K62" s="8">
-        <v>8.9829999999999993E-2</v>
+        <v>1.76491</v>
       </c>
       <c r="L62" s="4">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="M62" s="4">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="N62" s="8">
         <f t="shared" si="3"/>
-        <v>8.9829999999999988</v>
+        <v>8.8245500000000003</v>
       </c>
       <c r="O62" s="5" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
     </row>
     <row r="63" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
@@ -4682,25 +4731,25 @@
         <v>58</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="C63" s="4">
         <v>16</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="I63" s="6" t="s">
         <v>24</v>
@@ -4723,7 +4772,7 @@
         <v>5.9595000000000002</v>
       </c>
       <c r="O63" s="5" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="64" spans="1:15" ht="39.6" x14ac:dyDescent="0.3">
@@ -4731,46 +4780,48 @@
         <v>59</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C64" s="4">
         <v>16</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J64" s="7">
-        <v>0</v>
-      </c>
-      <c r="K64" s="8"/>
+        <v>342</v>
+      </c>
+      <c r="I64" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J64" s="21">
+        <v>857</v>
+      </c>
+      <c r="K64" s="8">
+        <v>6.8773900000000001</v>
+      </c>
       <c r="L64" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M64" s="4">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="N64" s="8" t="str">
+      <c r="N64" s="8">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="O64" s="5" t="s">
-        <v>353</v>
+        <v>220.07648</v>
+      </c>
+      <c r="O64" s="18" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -4778,25 +4829,25 @@
         <v>60</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="C65" s="4">
         <v>1</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>24</v>
@@ -4818,8 +4869,8 @@
         <f t="shared" si="3"/>
         <v>5.9050000000000002</v>
       </c>
-      <c r="O65" s="5" t="s">
-        <v>358</v>
+      <c r="O65" s="18" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
@@ -4827,25 +4878,25 @@
         <v>61</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C66" s="4">
         <v>1</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="I66" s="6" t="s">
         <v>24</v>
@@ -4868,7 +4919,7 @@
         <v>8.9829999999999988</v>
       </c>
       <c r="O66" s="5" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
     </row>
     <row r="67" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -4876,25 +4927,25 @@
         <v>62</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C67" s="4">
         <v>2</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="I67" s="6" t="s">
         <v>24</v>
@@ -4917,7 +4968,7 @@
         <v>14.541119999999999</v>
       </c>
       <c r="O67" s="5" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
@@ -4925,25 +4976,25 @@
         <v>63</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="I68" s="6" t="s">
         <v>24</v>
@@ -4966,7 +5017,7 @@
         <v>41.488399999999999</v>
       </c>
       <c r="O68" s="5" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -4974,34 +5025,34 @@
         <v>64</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="C69" s="4">
         <v>3</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="I69" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J69" s="7">
-        <v>0</v>
+        <v>369</v>
+      </c>
+      <c r="I69" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J69" s="21">
+        <v>93</v>
       </c>
       <c r="K69" s="8">
-        <v>5.4816599999999998</v>
+        <v>14.28</v>
       </c>
       <c r="L69" s="4">
         <v>5</v>
@@ -5012,10 +5063,10 @@
       </c>
       <c r="N69" s="8">
         <f t="shared" si="3"/>
-        <v>32.889960000000002</v>
-      </c>
-      <c r="O69" s="5" t="s">
-        <v>382</v>
+        <v>85.679999999999993</v>
+      </c>
+      <c r="O69" s="18" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
@@ -5023,48 +5074,48 @@
         <v>65</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="C70" s="4">
         <v>1</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="I70" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J70" s="7">
-        <v>0</v>
+        <v>374</v>
+      </c>
+      <c r="I70" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="J70" s="24" t="s">
+        <v>250</v>
       </c>
       <c r="K70" s="8">
-        <v>173.315</v>
+        <v>421.52</v>
       </c>
       <c r="L70" s="4">
         <v>1</v>
       </c>
       <c r="M70" s="4">
-        <f t="shared" ref="M70:M101" si="4">IF(L70="",C70*$C$3,MAX(C70*$C$3,L70))</f>
+        <f t="shared" ref="M70:M76" si="4">IF(L70="",C70*$C$3,MAX(C70*$C$3,L70))</f>
         <v>2</v>
       </c>
       <c r="N70" s="8">
-        <f t="shared" ref="N70:N101" si="5">IF(K70="","",K70*M70)</f>
-        <v>346.63</v>
-      </c>
-      <c r="O70" s="5" t="s">
-        <v>388</v>
+        <f t="shared" ref="N70:N77" si="5">IF(K70="","",K70*M70)</f>
+        <v>843.04</v>
+      </c>
+      <c r="O70" s="18" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
@@ -5072,25 +5123,25 @@
         <v>66</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="C71" s="4">
         <v>1</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>392</v>
+        <v>378</v>
       </c>
       <c r="I71" s="6" t="s">
         <v>24</v>
@@ -5113,7 +5164,7 @@
         <v>72.492400000000004</v>
       </c>
       <c r="O71" s="5" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
@@ -5121,25 +5172,25 @@
         <v>67</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="C72" s="4">
         <v>1</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>396</v>
+        <v>382</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>398</v>
+        <v>384</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="I72" s="6" t="s">
         <v>24</v>
@@ -5168,25 +5219,25 @@
         <v>68</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="C73" s="4">
         <v>1</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="I73" s="6" t="s">
         <v>24</v>
@@ -5215,25 +5266,25 @@
         <v>69</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="C74" s="4">
         <v>1</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>24</v>
@@ -5256,7 +5307,7 @@
         <v>24.315200000000001</v>
       </c>
       <c r="O74" s="5" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
     </row>
     <row r="75" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -5264,30 +5315,30 @@
         <v>70</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="C75" s="4">
         <v>1</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="I75" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J75" s="7">
+        <v>401</v>
+      </c>
+      <c r="I75" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="J75" s="21">
         <v>0</v>
       </c>
       <c r="K75" s="8"/>
@@ -5303,7 +5354,7 @@
         <v/>
       </c>
       <c r="O75" s="5" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:15" ht="26.4" x14ac:dyDescent="0.3">
@@ -5311,34 +5362,34 @@
         <v>71</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="C76" s="4">
         <v>1</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="I76" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J76" s="4">
-        <v>2955</v>
+      <c r="J76" s="23" t="s">
+        <v>250</v>
       </c>
       <c r="K76" s="8">
-        <v>7.0458400000000001</v>
+        <v>46.28</v>
       </c>
       <c r="L76" s="4">
         <v>1</v>
@@ -5349,10 +5400,10 @@
       </c>
       <c r="N76" s="8">
         <f t="shared" si="5"/>
-        <v>14.09168</v>
+        <v>92.56</v>
       </c>
       <c r="O76" s="5" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
@@ -5360,25 +5411,25 @@
         <v>72</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="C77" s="4">
         <v>2</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="I77" s="6" t="s">
         <v>24</v>
@@ -5400,7 +5451,7 @@
         <v>0</v>
       </c>
       <c r="O77" s="5" t="s">
-        <v>425</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.3">
@@ -5417,11 +5468,11 @@
       <c r="K78" s="8"/>
       <c r="L78" s="4"/>
       <c r="M78" s="9" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="N78" s="10">
         <f>SUM(N6:N77)</f>
-        <v>3213.208500000002</v>
+        <v>4107.377370000002</v>
       </c>
       <c r="O78" s="5"/>
     </row>
@@ -5444,7 +5495,7 @@
     </row>
     <row r="80" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80" s="11" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="B80" s="5"/>
       <c r="C80" s="4"/>
@@ -5466,13 +5517,13 @@
         <v>3</v>
       </c>
       <c r="B81" s="13" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>5</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="E81" s="13" t="s">
         <v>7</v>
@@ -5511,23 +5562,23 @@
         <v>1</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C82" s="4">
         <v>1</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="F82" s="4"/>
       <c r="G82" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>24</v>
@@ -5556,23 +5607,23 @@
         <v>2</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C83" s="4">
         <v>1</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>434</v>
+        <v>420</v>
       </c>
       <c r="F83" s="4"/>
       <c r="G83" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>24</v>
@@ -5601,23 +5652,23 @@
         <v>3</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C84" s="4">
         <v>1</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="F84" s="4"/>
       <c r="G84" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>438</v>
+        <v>424</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>24</v>
@@ -5646,23 +5697,23 @@
         <v>4</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C85" s="4">
         <v>1</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>439</v>
+        <v>425</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="F85" s="4"/>
       <c r="G85" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>24</v>
@@ -5691,23 +5742,23 @@
         <v>5</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C86" s="4">
         <v>1</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="F86" s="4"/>
       <c r="G86" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>444</v>
+        <v>430</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>24</v>
@@ -5736,23 +5787,23 @@
         <v>6</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="C87" s="4">
         <v>2</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>446</v>
+        <v>432</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>447</v>
+        <v>433</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>24</v>
@@ -5775,7 +5826,7 @@
         <v>3.4437000000000002</v>
       </c>
       <c r="O87" s="5" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
@@ -5792,7 +5843,7 @@
       <c r="K88" s="8"/>
       <c r="L88" s="4"/>
       <c r="M88" s="9" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="N88" s="10">
         <f>SUM(N82:N87)</f>
@@ -5819,7 +5870,7 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="15" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="B90" s="5"/>
       <c r="C90" s="4"/>
@@ -5838,7 +5889,7 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A91" s="15" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="B91" s="5"/>
       <c r="C91" s="4"/>
@@ -5925,12 +5976,12 @@
     <hyperlink ref="I67" r:id="rId61" xr:uid="{00000000-0004-0000-0000-00003C000000}"/>
     <hyperlink ref="I68" r:id="rId62" xr:uid="{00000000-0004-0000-0000-00003D000000}"/>
     <hyperlink ref="I69" r:id="rId63" xr:uid="{00000000-0004-0000-0000-00003E000000}"/>
-    <hyperlink ref="I70" r:id="rId64" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
+    <hyperlink ref="I70" r:id="rId64" display="Özdisan" xr:uid="{00000000-0004-0000-0000-00003F000000}"/>
     <hyperlink ref="I71" r:id="rId65" xr:uid="{00000000-0004-0000-0000-000040000000}"/>
     <hyperlink ref="I72" r:id="rId66" xr:uid="{00000000-0004-0000-0000-000041000000}"/>
     <hyperlink ref="I73" r:id="rId67" xr:uid="{00000000-0004-0000-0000-000042000000}"/>
     <hyperlink ref="I74" r:id="rId68" xr:uid="{00000000-0004-0000-0000-000043000000}"/>
-    <hyperlink ref="I75" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
+    <hyperlink ref="I75" r:id="rId69" display="Özdisan" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
     <hyperlink ref="I76" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
     <hyperlink ref="I77" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
     <hyperlink ref="I82" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>

--- a/Hardware/BMS_V4/BOM/BMS_V4.02_BOM.xlsx
+++ b/Hardware/BMS_V4/BOM/BMS_V4.02_BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Electronics_Solaris\BMS Version 4\Hardware\BMS_V4\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\01 Git Repos\BMS-Version-4\Hardware\BMS_V4\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47A7EEAA-35EC-4A3A-BAD8-AABD4FFD25E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -1527,7 +1527,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1579,23 +1579,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1881,26 +1872,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="A2" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2712,7 +2703,7 @@
       <c r="I21" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J21" s="21">
+      <c r="J21" s="4">
         <v>1200</v>
       </c>
       <c r="K21" s="8">
@@ -2810,7 +2801,7 @@
       <c r="I23" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J23" s="21">
+      <c r="J23" s="4">
         <v>8800</v>
       </c>
       <c r="K23" s="8">
@@ -3006,7 +2997,7 @@
       <c r="I27" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J27" s="21">
+      <c r="J27" s="4">
         <v>10000</v>
       </c>
       <c r="K27" s="8">
@@ -3594,10 +3585,10 @@
       <c r="I39" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J39" s="21">
+      <c r="J39" s="4">
         <v>242</v>
       </c>
-      <c r="K39" s="22">
+      <c r="K39" s="8">
         <v>5.5145900000000001</v>
       </c>
       <c r="L39" s="4">
@@ -3923,7 +3914,7 @@
       <c r="E46" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="F46" s="23" t="s">
+      <c r="F46" s="19" t="s">
         <v>249</v>
       </c>
       <c r="G46" s="4" t="s">
@@ -4803,7 +4794,7 @@
       <c r="I64" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J64" s="21">
+      <c r="J64" s="4">
         <v>857</v>
       </c>
       <c r="K64" s="8">
@@ -5048,7 +5039,7 @@
       <c r="I69" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J69" s="21">
+      <c r="J69" s="4">
         <v>93</v>
       </c>
       <c r="K69" s="8">
@@ -5097,7 +5088,7 @@
       <c r="I70" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="J70" s="24" t="s">
+      <c r="J70" s="19" t="s">
         <v>250</v>
       </c>
       <c r="K70" s="8">
@@ -5338,7 +5329,7 @@
       <c r="I75" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="J75" s="21">
+      <c r="J75" s="4">
         <v>0</v>
       </c>
       <c r="K75" s="8"/>
@@ -5385,7 +5376,7 @@
       <c r="I76" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J76" s="23" t="s">
+      <c r="J76" s="19" t="s">
         <v>250</v>
       </c>
       <c r="K76" s="8">
